--- a/Excels/ParameterRanges.xlsx
+++ b/Excels/ParameterRanges.xlsx
@@ -2441,13 +2441,13 @@
         <v>Interval (Sec)</v>
       </c>
       <c r="D71">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="E71">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="F71">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G71">
         <v>0.1</v>
